--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G42">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G47">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G54">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G74">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G81">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G117">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G128">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G54">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G73">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G74">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G91">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G113">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G117">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G42">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G132">

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q29">
         <v>0</v>

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q96">
         <v>0</v>

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G19">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q100">
         <v>0</v>

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G15">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G71">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G82">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G90">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G91">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G131">

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU132"/>
+  <dimension ref="A1:AU131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-11-06 10:30:00</t>
+          <t>2026-11-06 11:00:00</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-11-06 11:00:00</t>
+          <t>2026-11-06 11:15:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-11-06 11:15:00</t>
+          <t>2026-11-06 11:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-11-06 11:30:00</t>
+          <t>2026-11-06 11:55:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-11-06 11:55:00</t>
+          <t>2026-11-06 12:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-11-06 12:00:00</t>
+          <t>2026-11-06 12:30:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-11-06 12:30:00</t>
+          <t>2026-11-06 13:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-11-06 13:00:00</t>
+          <t>2026-11-06 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O34">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-11-06 13:30:00</t>
+          <t>2026-11-06 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-11-06 14:00:00</t>
+          <t>2026-11-06 14:15:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-11-06 14:15:00</t>
+          <t>2026-11-06 14:30:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="O55">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P55">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-11-06 14:30:00</t>
+          <t>2026-11-06 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.55</v>
+        <v>1.19</v>
       </c>
       <c r="O61">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="P61">
-        <v>2.48</v>
+        <v>11.7</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-11-06 15:00:00</t>
+          <t>2026-11-06 15:30:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.19</v>
+        <v>2.23</v>
       </c>
       <c r="O62">
-        <v>6.8</v>
+        <v>3.78</v>
       </c>
       <c r="P62">
-        <v>11.7</v>
+        <v>2.47</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AD62">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="AE62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.23</v>
+        <v>7.13</v>
       </c>
       <c r="O63">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="P63">
-        <v>2.47</v>
+        <v>1.32</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AD63">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-11-06 15:30:00</t>
+          <t>2026-11-06 15:45:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-11-06 15:45:00</t>
+          <t>2026-11-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="P74">
-        <v>2.55</v>
+        <v>2.16</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-11-06 16:00:00</t>
+          <t>2026-11-06 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-11-06 16:15:00</t>
+          <t>2026-11-06 16:30:00</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P86">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.65</v>
+        <v>1.88</v>
       </c>
       <c r="O88">
-        <v>4.26</v>
+        <v>3.68</v>
       </c>
       <c r="P88">
-        <v>4.98</v>
+        <v>3.63</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15187,10 +15187,10 @@
         <v>0</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE91">
         <v>0</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P92">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15350,10 +15350,10 @@
         <v>0</v>
       </c>
       <c r="AC92">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-11-06 16:30:00</t>
+          <t>2026-11-06 16:45:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="O96">
-        <v>3.98</v>
+        <v>4.36</v>
       </c>
       <c r="P96">
-        <v>4.24</v>
+        <v>4.98</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-11-06 16:45:00</t>
+          <t>2026-11-06 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="P97">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB97">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O99">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P99">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P100">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-11-06 17:00:00</t>
+          <t>2026-11-06 17:15:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-11-06 17:15:00</t>
+          <t>2026-11-06 17:45:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-11-06 17:45:00</t>
+          <t>2026-11-06 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O104">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P104">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-11-06 19:30:00</t>
+          <t>2026-11-06 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O105">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P105">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-11-06 20:00:00</t>
+          <t>2026-11-06 21:00:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G114">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G131">
@@ -21765,169 +21765,6 @@
         <v>0</v>
       </c>
       <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-11-06 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
         <is>
           <t>2026-11-06 21:00:00</t>
         </is>

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G131">

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G116">

--- a/jogos_2026-11-06.xlsx
+++ b/jogos_2026-11-06.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU131"/>
+  <dimension ref="A1:AU129"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="G7">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="G9">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arema</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="G10">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Arema</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-11-06 10:00:00</t>
+          <t>2026-11-06 09:00:00</t>
         </is>
       </c>
     </row>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Kiryat Gat</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maccabi Ahi Nazareth</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Maccabi Ahi Nazareth</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G19">
@@ -3522,27 +3522,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-11-06 10:30:00</t>
+          <t>2026-11-06 10:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,27 +3685,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-11-06 11:00:00</t>
+          <t>2026-11-06 10:30:00</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G24">
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-11-06 11:15:00</t>
+          <t>2026-11-06 11:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-11-06 11:30:00</t>
+          <t>2026-11-06 11:15:00</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-11-06 11:55:00</t>
+          <t>2026-11-06 11:30:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-11-06 12:00:00</t>
+          <t>2026-11-06 11:55:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-11-06 12:30:00</t>
+          <t>2026-11-06 12:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-11-06 13:00:00</t>
+          <t>2026-11-06 12:30:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-11-06 13:30:00</t>
+          <t>2026-11-06 13:00:00</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="G32">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-11-06 14:00:00</t>
+          <t>2026-11-06 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Gaziantep FK</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="G36">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Gaziantep FK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G40">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G41">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nea Salamis</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Omonia Aradippou</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AEK Larnaca</t>
+          <t>Nea Salamis</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Karmiotissa</t>
+          <t>Omonia Aradippou</t>
         </is>
       </c>
       <c r="G48">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Karmiotissa</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-11-06 14:15:00</t>
+          <t>2026-11-06 14:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,12 +8412,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-11-06 14:30:00</t>
+          <t>2026-11-06 14:15:00</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="O55">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P55">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9319,10 +9319,10 @@
         <v>0</v>
       </c>
       <c r="AC55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE55">
         <v>0</v>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9482,10 +9482,10 @@
         <v>0</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-11-06 15:00:00</t>
+          <t>2026-11-06 14:30:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G57">
@@ -9721,22 +9721,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9884,22 +9884,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hassania Agadir</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Hassania Agadir</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.19</v>
+        <v>2.55</v>
       </c>
       <c r="O61">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="P61">
-        <v>11.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10297,10 +10297,10 @@
         <v>0</v>
       </c>
       <c r="AC61">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD61">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-11-06 15:30:00</t>
+          <t>2026-11-06 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kriens</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.23</v>
+        <v>1.19</v>
       </c>
       <c r="O62">
-        <v>3.78</v>
+        <v>6.8</v>
       </c>
       <c r="P62">
-        <v>2.47</v>
+        <v>11.7</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10460,10 +10460,10 @@
         <v>0</v>
       </c>
       <c r="AC62">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AD62">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AE62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Kriens</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>7.13</v>
+        <v>2.23</v>
       </c>
       <c r="O63">
-        <v>4.8</v>
+        <v>3.78</v>
       </c>
       <c r="P63">
-        <v>1.32</v>
+        <v>2.47</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10623,10 +10623,10 @@
         <v>0</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-11-06 15:45:00</t>
+          <t>2026-11-06 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-11-06 16:00:00</t>
+          <t>2026-11-06 15:45:00</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G67">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G68">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G69">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G70">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="G71">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G72">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting Hasselt</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P73">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sporting Hasselt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="O74">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G77">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G78">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G80">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G81">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G82">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-11-06 16:15:00</t>
+          <t>2026-11-06 16:00:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G83">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-11-06 16:30:00</t>
+          <t>2026-11-06 16:15:00</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Unia Skierniewice</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Unia Skierniewice</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P85">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,13 +14490,13 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="P87">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="Q87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="O88">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="P88">
-        <v>3.63</v>
+        <v>4.98</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,13 +14816,13 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="Q89">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G90">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15187,10 +15187,10 @@
         <v>0</v>
       </c>
       <c r="AC91">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD91">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE91">
         <v>0</v>
@@ -15258,12 +15258,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15350,10 +15350,10 @@
         <v>0</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE92">
         <v>0</v>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-11-06 16:45:00</t>
+          <t>2026-11-06 16:30:00</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Toulouse</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Toulouse</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="O94">
-        <v>3.52</v>
+        <v>3.97</v>
       </c>
       <c r="P94">
-        <v>3.11</v>
+        <v>3.68</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,13 +15794,13 @@
         </is>
       </c>
       <c r="N95">
-        <v>1.79</v>
+        <v>2.44</v>
       </c>
       <c r="O95">
-        <v>3.98</v>
+        <v>3.52</v>
       </c>
       <c r="P95">
-        <v>4.24</v>
+        <v>3.11</v>
       </c>
       <c r="Q95">
         <v>0</v>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,13 +15957,13 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="O96">
-        <v>4.36</v>
+        <v>3.98</v>
       </c>
       <c r="P96">
-        <v>4.98</v>
+        <v>4.24</v>
       </c>
       <c r="Q96">
         <v>0</v>
@@ -15996,10 +15996,10 @@
         <v>0</v>
       </c>
       <c r="AA96">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB96">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC96">
         <v>0</v>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-11-06 17:00:00</t>
+          <t>2026-11-06 16:45:00</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,13 +16446,13 @@
         </is>
       </c>
       <c r="N99">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P99">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q99">
         <v>0</v>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Amal Tiznit</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,13 +16609,13 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q100">
         <v>0</v>
@@ -16725,12 +16725,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Real Avilés</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Amal Tiznit</t>
         </is>
       </c>
       <c r="G101">
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-11-06 17:15:00</t>
+          <t>2026-11-06 17:00:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Famalicão</t>
+          <t>Real Avilés</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G102">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-11-06 17:45:00</t>
+          <t>2026-11-06 17:15:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Famalicão</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="G103">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-11-06 19:30:00</t>
+          <t>2026-11-06 17:45:00</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17214,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G104">
@@ -17261,13 +17261,13 @@
         </is>
       </c>
       <c r="N104">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="P104">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q104">
         <v>0</v>
@@ -17365,7 +17365,7 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>2026-11-06 20:00:00</t>
+          <t>2026-11-06 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17540,27 +17540,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="G106">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>2026-11-06 21:00:00</t>
+          <t>2026-11-06 20:00:00</t>
         </is>
       </c>
     </row>
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G114">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G129">
@@ -21439,332 +21439,6 @@
         <v>0</v>
       </c>
       <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-11-06 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Naftagas</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
-      <c r="O130">
-        <v>0</v>
-      </c>
-      <c r="P130">
-        <v>0</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>0</v>
-      </c>
-      <c r="AB130">
-        <v>0</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-11-06 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-11-06</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
         <is>
           <t>2026-11-06 21:00:00</t>
         </is>
